--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.171.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.171.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -883,7 +883,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.171.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.171.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y50"/>
+  <dimension ref="A1:Y52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.171.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.171.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0171.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0171.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -601,16 +601,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L18: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR :: May issue Subp Ã¦ na, to add new parties</t>
+          <t>L39: stray/suspicious non-ASCII glyph(s): U+2605 BLACK STAR | isolated marker/symbol line :: ★</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L18: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: MASTERâ€™S OFFICEâ€”Continued.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]164</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]164</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L1: isolated marker/symbol line :: 164</t>
@@ -618,7 +622,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L8: isolated marker/symbol line :: s</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]164</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>87</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -668,12 +672,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L39: stray/suspicious non-ASCII glyph(s): U+02DC SMALL TILDE | isolated marker/symbol line :: â˜…</t>
+          <t>L45: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 103â€”104</t>
+          <t>L140: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -685,7 +689,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L11: isolated marker/symbol line :: E</t>
+          <t>L8: isolated marker/symbol line :: s</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -731,12 +735,12 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L48: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 3 â€” 4</t>
+          <t>L80: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L120: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 86â€”87</t>
+          <t>L148: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -748,7 +752,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L13: isolated marker/symbol line :: S</t>
+          <t>L11: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -788,16 +792,8 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L140: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
@@ -807,7 +803,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L14: isolated marker/symbol line :: C</t>
+          <t>L13: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -848,11 +844,7 @@
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
       <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L148: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -862,7 +854,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L16: isolated marker/symbol line :: V</t>
+          <t>L14: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -913,7 +905,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L46: isolated marker/symbol line :: 94</t>
+          <t>L16: isolated marker/symbol line :: V</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -960,7 +952,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L48: isolated marker/symbol line :: 94</t>
+          <t>L46: isolated marker/symbol line :: 94</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1007,7 +999,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L56: isolated marker/symbol line :: 0</t>
+          <t>L48: isolated marker/symbol line :: 94</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1029,12 +1021,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1054,7 +1046,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L60: isolated marker/symbol line :: 146</t>
+          <t>L54: symbol-only separator/garbage line :: 103—104</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1081,7 +1073,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1101,7 +1093,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L62: symbol-only separator/garbage line :: . 142</t>
+          <t>L56: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1123,12 +1115,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1148,7 +1140,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L64: isolated marker/symbol line :: P</t>
+          <t>L60: isolated marker/symbol line :: 146</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1195,7 +1187,7 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: C</t>
+          <t>L62: symbol-only separator/garbage line :: . 142</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1242,7 +1234,7 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L69: isolated marker/symbol line :: I</t>
+          <t>L64: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1289,7 +1281,7 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: E</t>
+          <t>L67: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1336,7 +1328,7 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: T</t>
+          <t>L69: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1383,7 +1375,7 @@
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: v</t>
+          <t>L70: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1418,7 +1410,7 @@
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: 0</t>
+          <t>L72: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1453,7 +1445,7 @@
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L78: isolated marker/symbol line :: 0</t>
+          <t>L73: isolated marker/symbol line :: v</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1483,12 +1475,12 @@
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L39: stray/suspicious non-ASCII glyph(s): U+02DC SMALL TILDE | isolated marker/symbol line :: â˜…</t>
+          <t>L39: stray/suspicious non-ASCII glyph(s): U+2605 BLACK STAR | isolated marker/symbol line :: ★</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: R</t>
+          <t>L76: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1523,7 +1515,7 @@
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: C</t>
+          <t>L78: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1558,7 +1550,7 @@
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L88: isolated marker/symbol line :: N</t>
+          <t>L82: isolated marker/symbol line :: R</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1588,12 +1580,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L46: isolated marker/symbol line :: 3</t>
+          <t>L45: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: E</t>
+          <t>L84: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1623,12 +1615,12 @@
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L51: symbol-only separator/garbage line :: . 86-87</t>
+          <t>L46: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L91: isolated marker/symbol line :: 0</t>
+          <t>L88: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1658,12 +1650,12 @@
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: 155</t>
+          <t>L48: symbol-only separator/garbage line :: 3 — 4</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: 0</t>
+          <t>L90: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1693,12 +1685,12 @@
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L56: isolated marker/symbol line :: . 0</t>
+          <t>L51: symbol-only separator/garbage line :: . 86-87</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: 114</t>
+          <t>L91: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1728,12 +1720,12 @@
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L57: isolated marker/symbol line :: D</t>
+          <t>L53: isolated marker/symbol line :: 155</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L116: isolated marker/symbol line :: 110</t>
+          <t>L94: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1763,12 +1755,12 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L58: isolated marker/symbol line :: E</t>
+          <t>L56: isolated marker/symbol line :: . 0</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L118: isolated marker/symbol line :: ,</t>
+          <t>L96: isolated marker/symbol line :: 114</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1798,12 +1790,12 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L59: isolated marker/symbol line :: T</t>
+          <t>L57: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L122: symbol-only separator/garbage line :: .155</t>
+          <t>L116: isolated marker/symbol line :: 110</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1833,12 +1825,12 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L60: isolated marker/symbol line :: V</t>
+          <t>L58: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L124: symbol-only separator/garbage line :: . 105</t>
+          <t>L118: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1868,12 +1860,12 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L62: isolated marker/symbol line :: 0</t>
+          <t>L59: isolated marker/symbol line :: T</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L125: isolated marker/symbol line :: 116</t>
+          <t>L120: symbol-only separator/garbage line :: . 86—87</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1903,12 +1895,12 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: 0</t>
+          <t>L60: isolated marker/symbol line :: V</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L140: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L122: symbol-only separator/garbage line :: .155</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -1938,12 +1930,12 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: R</t>
+          <t>L62: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L142: isolated marker/symbol line :: 1</t>
+          <t>L124: symbol-only separator/garbage line :: . 105</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -1973,12 +1965,12 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L66: isolated marker/symbol line :: ,</t>
+          <t>L63: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
         <is>
-          <t>L144: isolated marker/symbol line :: 1</t>
+          <t>L125: isolated marker/symbol line :: 116</t>
         </is>
       </c>
       <c r="P34" s="1" t="inlineStr"/>
@@ -2008,12 +2000,12 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L68: isolated marker/symbol line :: 105</t>
+          <t>L65: isolated marker/symbol line :: R</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
         <is>
-          <t>L146: isolated marker/symbol line :: 1</t>
+          <t>L140: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P35" s="1" t="inlineStr"/>
@@ -2043,12 +2035,12 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: 116</t>
+          <t>L66: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
         <is>
-          <t>L148: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L142: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P36" s="1" t="inlineStr"/>
@@ -2078,12 +2070,12 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L73: isolated marker/symbol line :: 105</t>
+          <t>L68: isolated marker/symbol line :: 105</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
         <is>
-          <t>L150: isolated marker/symbol line :: .2</t>
+          <t>L144: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P37" s="1" t="inlineStr"/>
@@ -2113,12 +2105,12 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: 1</t>
+          <t>L70: isolated marker/symbol line :: 116</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
         <is>
-          <t>L157: isolated marker/symbol line :: C</t>
+          <t>L146: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P38" s="1" t="inlineStr"/>
@@ -2148,12 +2140,12 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L80: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L73: isolated marker/symbol line :: 105</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr">
         <is>
-          <t>L158: isolated marker/symbol line | line starts with punctuation glued to text :: .E</t>
+          <t>L148: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P39" s="1" t="inlineStr"/>
@@ -2183,10 +2175,14 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: .</t>
-        </is>
-      </c>
-      <c r="O40" s="1" t="inlineStr"/>
+          <t>L77: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O40" s="1" t="inlineStr">
+        <is>
+          <t>L150: isolated marker/symbol line :: .2</t>
+        </is>
+      </c>
       <c r="P40" s="1" t="inlineStr"/>
       <c r="Q40" s="1" t="inlineStr"/>
       <c r="R40" s="1" t="inlineStr"/>
@@ -2214,10 +2210,14 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: 2</t>
-        </is>
-      </c>
-      <c r="O41" s="1" t="inlineStr"/>
+          <t>L80: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="O41" s="1" t="inlineStr">
+        <is>
+          <t>L157: isolated marker/symbol line :: C</t>
+        </is>
+      </c>
       <c r="P41" s="1" t="inlineStr"/>
       <c r="Q41" s="1" t="inlineStr"/>
       <c r="R41" s="1" t="inlineStr"/>
@@ -2245,10 +2245,14 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L85: symbol-only separator/garbage line :: 5-6</t>
-        </is>
-      </c>
-      <c r="O42" s="1" t="inlineStr"/>
+          <t>L81: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O42" s="1" t="inlineStr">
+        <is>
+          <t>L158: isolated marker/symbol line | line starts with punctuation glued to text :: .E</t>
+        </is>
+      </c>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr"/>
       <c r="R42" s="1" t="inlineStr"/>
@@ -2276,7 +2280,7 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L87: isolated marker/symbol line :: C</t>
+          <t>L82: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr"/>
@@ -2307,7 +2311,7 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: N</t>
+          <t>L85: symbol-only separator/garbage line :: 5-6</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr"/>
@@ -2338,7 +2342,7 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: E</t>
+          <t>L87: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr"/>
@@ -2369,7 +2373,7 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L91: isolated marker/symbol line :: 0</t>
+          <t>L89: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -2400,7 +2404,7 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: O</t>
+          <t>L90: isolated marker/symbol line :: E</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -2431,7 +2435,7 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: 0</t>
+          <t>L91: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -2462,7 +2466,7 @@
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: C</t>
+          <t>L92: isolated marker/symbol line :: O</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -2493,7 +2497,7 @@
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: . E</t>
+          <t>L94: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -2508,6 +2512,68 @@
       <c r="X50" s="1" t="inlineStr"/>
       <c r="Y50" s="1" t="inlineStr"/>
     </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr"/>
+      <c r="B51" s="1" t="inlineStr"/>
+      <c r="C51" s="1" t="inlineStr"/>
+      <c r="D51" s="1" t="inlineStr"/>
+      <c r="E51" s="1" t="inlineStr"/>
+      <c r="F51" s="1" t="inlineStr"/>
+      <c r="G51" s="1" t="inlineStr"/>
+      <c r="H51" s="1" t="inlineStr"/>
+      <c r="I51" s="1" t="inlineStr"/>
+      <c r="J51" s="1" t="inlineStr"/>
+      <c r="K51" s="1" t="inlineStr"/>
+      <c r="L51" s="1" t="inlineStr"/>
+      <c r="M51" s="1" t="inlineStr"/>
+      <c r="N51" s="1" t="inlineStr">
+        <is>
+          <t>L95: isolated marker/symbol line :: C</t>
+        </is>
+      </c>
+      <c r="O51" s="1" t="inlineStr"/>
+      <c r="P51" s="1" t="inlineStr"/>
+      <c r="Q51" s="1" t="inlineStr"/>
+      <c r="R51" s="1" t="inlineStr"/>
+      <c r="S51" s="1" t="inlineStr"/>
+      <c r="T51" s="1" t="inlineStr"/>
+      <c r="U51" s="1" t="inlineStr"/>
+      <c r="V51" s="1" t="inlineStr"/>
+      <c r="W51" s="1" t="inlineStr"/>
+      <c r="X51" s="1" t="inlineStr"/>
+      <c r="Y51" s="1" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr"/>
+      <c r="B52" s="1" t="inlineStr"/>
+      <c r="C52" s="1" t="inlineStr"/>
+      <c r="D52" s="1" t="inlineStr"/>
+      <c r="E52" s="1" t="inlineStr"/>
+      <c r="F52" s="1" t="inlineStr"/>
+      <c r="G52" s="1" t="inlineStr"/>
+      <c r="H52" s="1" t="inlineStr"/>
+      <c r="I52" s="1" t="inlineStr"/>
+      <c r="J52" s="1" t="inlineStr"/>
+      <c r="K52" s="1" t="inlineStr"/>
+      <c r="L52" s="1" t="inlineStr"/>
+      <c r="M52" s="1" t="inlineStr"/>
+      <c r="N52" s="1" t="inlineStr">
+        <is>
+          <t>L96: isolated marker/symbol line :: . E</t>
+        </is>
+      </c>
+      <c r="O52" s="1" t="inlineStr"/>
+      <c r="P52" s="1" t="inlineStr"/>
+      <c r="Q52" s="1" t="inlineStr"/>
+      <c r="R52" s="1" t="inlineStr"/>
+      <c r="S52" s="1" t="inlineStr"/>
+      <c r="T52" s="1" t="inlineStr"/>
+      <c r="U52" s="1" t="inlineStr"/>
+      <c r="V52" s="1" t="inlineStr"/>
+      <c r="W52" s="1" t="inlineStr"/>
+      <c r="X52" s="1" t="inlineStr"/>
+      <c r="Y52" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
